--- a/covid_19_report_forms/005_student_covid_19_self_certification_and_verification_form--covid_19_report_forms.xlsx
+++ b/covid_19_report_forms/005_student_covid_19_self_certification_and_verification_form--covid_19_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>sore throat</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>shortness_of_breath</t>
+          <t>shortness of breath</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>muscle_pains</t>
+          <t>muscle pains</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>new_loss_of_smell</t>
+          <t>new loss of smell</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>new_loss_of_taste</t>
+          <t>new loss of taste</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nausea_vomiting</t>
+          <t>nausea vomiting</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sore_throat</t>
+          <t>fatigue</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>difficulty_breathing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>fatigue</t>
+          <t>difficulty breathing</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>difficulty_breathing</t>
+          <t>loss of appetite</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>runny_nose</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>runny nose</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>congestion</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>runny_nose</t>
+          <t>congestion</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>congestion</t>
+          <t>loss_of_speech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>congestion</t>
+          <t>loss of speech</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>loss_of_speech</t>
+          <t>loss_of_taste</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>loss_of_speech</t>
+          <t>loss of taste</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss_of_smell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>loss_of_taste</t>
+          <t>loss of smell</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>chest_tightness</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>loss_of_smell</t>
+          <t>chest tightness</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>chest_tightness</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chest_tightness</t>
+          <t>chest pain</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>loss_of_energy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>chest_pain</t>
+          <t>loss of energy</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>loss_of_energy</t>
+          <t>loss_of_concentration</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>loss_of_energy</t>
+          <t>loss of concentration</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>loss_of_concentration</t>
+          <t>loss_of_sleep</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>loss_of_concentration</t>
+          <t>loss of sleep</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>loss_of_sleep</t>
+          <t>loss_of_memory</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>loss_of_sleep</t>
+          <t>loss of memory</t>
         </is>
       </c>
     </row>
@@ -1573,53 +1573,53 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>loss_of_memory</t>
+          <t>loss_of_saliva</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>loss_of_memory</t>
+          <t>loss of saliva</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>loss_of_appetite</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>loss_of_saliva</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>loss_of_saliva</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>question_13_choices</t>
+          <t>question_14_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>question_14_choices</t>
+          <t>question_15_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2078,7 +2078,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2095,7 +2095,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>question_17_choices</t>
+          <t>question_18_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_19_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2214,7 +2214,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>question_19_choices</t>
+          <t>question_20_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>question_20_choices</t>
+          <t>question_21_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>question_21_choices</t>
+          <t>question_22_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2291,40 +2291,6 @@
         </is>
       </c>
       <c r="C70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
         <is>
           <t>False</t>
         </is>
